--- a/outputs/382-10.xlsx
+++ b/outputs/382-10.xlsx
@@ -156,12 +156,16 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -169,7 +173,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -426,70 +430,70 @@
   <dimension ref="A1:A18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
+      <c r="A2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
+      <c r="A4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
+      <c r="A5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
+      <c r="A6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
+      <c r="A7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
+      <c r="A9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
+      <c r="A10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
+      <c r="A11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
+      <c r="A13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
+      <c r="A14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
+      <c r="A15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
+      <c r="A16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
+      <c r="A17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
+      <c r="A18" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
